--- a/main/ig/mappingmodelemetierCDAFHIR.xlsx
+++ b/main/ig/mappingmodelemetierCDAFHIR.xlsx
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-23T15:44:19+00:00</t>
+    <t>2025-08-01T08:11:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/mappingmodelemetierCDAFHIR.xlsx
+++ b/main/ig/mappingmodelemetierCDAFHIR.xlsx
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-01T08:11:50+00:00</t>
+    <t>2025-08-22T10:16:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/mappingmodelemetierCDAFHIR.xlsx
+++ b/main/ig/mappingmodelemetierCDAFHIR.xlsx
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-22T10:16:53+00:00</t>
+    <t>2025-08-25T15:42:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/mappingmodelemetierCDAFHIR.xlsx
+++ b/main/ig/mappingmodelemetierCDAFHIR.xlsx
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-25T15:42:10+00:00</t>
+    <t>2025-10-02T14:05:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/mappingmodelemetierCDAFHIR.xlsx
+++ b/main/ig/mappingmodelemetierCDAFHIR.xlsx
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-02T14:05:03+00:00</t>
+    <t>2025-10-02T15:16:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/mappingmodelemetierCDAFHIR.xlsx
+++ b/main/ig/mappingmodelemetierCDAFHIR.xlsx
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-02T15:16:38+00:00</t>
+    <t>2025-10-13T15:21:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/mappingmodelemetierCDAFHIR.xlsx
+++ b/main/ig/mappingmodelemetierCDAFHIR.xlsx
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-13T15:21:05+00:00</t>
+    <t>2025-10-20T17:15:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/mappingmodelemetierCDAFHIR.xlsx
+++ b/main/ig/mappingmodelemetierCDAFHIR.xlsx
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-20T17:15:49+00:00</t>
+    <t>2025-10-21T08:14:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/mappingmodelemetierCDAFHIR.xlsx
+++ b/main/ig/mappingmodelemetierCDAFHIR.xlsx
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-21T08:14:34+00:00</t>
+    <t>2025-10-21T15:23:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/mappingmodelemetierCDAFHIR.xlsx
+++ b/main/ig/mappingmodelemetierCDAFHIR.xlsx
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-21T15:23:03+00:00</t>
+    <t>2025-10-21T16:49:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -107,16 +107,16 @@
     <t>Target</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/EnteteDocument</t>
+    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-entete-document</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-core-clinical-document</t>
-  </si>
-  <si>
-    <t>EnteteDocument.identifiantUniqueDocument</t>
+    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-cda-clinical-document</t>
+  </si>
+  <si>
+    <t>FRLMEnteteDocument.identifiantUniqueDocument</t>
   </si>
   <si>
     <t>equivalent</t>
@@ -125,139 +125,139 @@
     <t>ClinicalDocument.id</t>
   </si>
   <si>
-    <t>EnteteDocument.modeleDocument</t>
+    <t>FRLMEnteteDocument.modeleDocument</t>
   </si>
   <si>
     <t>ClinicalDocument.templateId</t>
   </si>
   <si>
-    <t>EnteteDocument.typeDocument</t>
+    <t>FRLMEnteteDocument.typeDocument</t>
   </si>
   <si>
     <t>ClinicalDocument.code</t>
   </si>
   <si>
-    <t>EnteteDocument.titreDocument</t>
+    <t>FRLMEnteteDocument.titreDocument</t>
   </si>
   <si>
     <t>ClinicalDocument.title</t>
   </si>
   <si>
-    <t>EnteteDocument.dateDeCreationDocument</t>
+    <t>FRLMEnteteDocument.dateDeCreationDocument</t>
   </si>
   <si>
     <t>ClinicalDocument.effectiveTime</t>
   </si>
   <si>
-    <t>EnteteDocument.niveauConfidentialiteDocument</t>
+    <t>FRLMEnteteDocument.niveauConfidentialiteDocument</t>
   </si>
   <si>
     <t>ClinicalDocument.confidentialityCode</t>
   </si>
   <si>
-    <t>EnteteDocument.languePrincipaleDocument</t>
+    <t>FRLMEnteteDocument.languePrincipaleDocument</t>
   </si>
   <si>
     <t>ClinicalDocument.languageCode</t>
   </si>
   <si>
-    <t>EnteteDocument.identifiantLotDeVersionsDocument</t>
+    <t>FRLMEnteteDocument.identifiantLotDeVersionsDocument</t>
   </si>
   <si>
     <t>ClinicalDocument.setId</t>
   </si>
   <si>
-    <t>EnteteDocument.versionDocument</t>
+    <t>FRLMEnteteDocument.versionDocument</t>
   </si>
   <si>
     <t>ClinicalDocument.versionNumber</t>
   </si>
   <si>
-    <t>EnteteDocument.StatutDocument</t>
+    <t>FRLMEnteteDocument.StatutDocument</t>
   </si>
   <si>
     <t>ClinicalDocument.documentationOf.serviceEvent.lab:statusCode</t>
   </si>
   <si>
-    <t>EnteteDocument.patient</t>
+    <t>FRLMEnteteDocument.patient</t>
   </si>
   <si>
     <t>ClinicalDocument.recordTarget</t>
   </si>
   <si>
-    <t>EnteteDocument.auteur</t>
+    <t>FRLMEnteteDocument.auteur</t>
   </si>
   <si>
     <t>ClinicalDocument.author</t>
   </si>
   <si>
-    <t>EnteteDocument.operateurSaisie</t>
+    <t>FRLMEnteteDocument.operateurSaisie</t>
   </si>
   <si>
     <t>ClinicalDocument.dataEnterer</t>
   </si>
   <si>
-    <t>EnteteDocument.informateur</t>
+    <t>FRLMEnteteDocument.informateur</t>
   </si>
   <si>
     <t>ClinicalDocument.informant</t>
   </si>
   <si>
-    <t>EnteteDocument.structureConservation</t>
+    <t>FRLMEnteteDocument.structureConservation</t>
   </si>
   <si>
     <t>ClinicalDocument.custodian</t>
   </si>
   <si>
-    <t>EnteteDocument.destinataire</t>
+    <t>FRLMEnteteDocument.destinataire</t>
   </si>
   <si>
     <t>ClinicalDocument.informationRecipient</t>
   </si>
   <si>
-    <t>EnteteDocument.responsable</t>
+    <t>FRLMEnteteDocument.responsable</t>
   </si>
   <si>
     <t>ClinicalDocument.legalAuthenticator</t>
   </si>
   <si>
-    <t>EnteteDocument.validateur</t>
+    <t>FRLMEnteteDocument.validateur</t>
   </si>
   <si>
     <t>ClinicalDocument.authenticator</t>
   </si>
   <si>
-    <t>EnteteDocument.participant</t>
+    <t>FRLMEnteteDocument.participant</t>
   </si>
   <si>
     <t>ClinicalDocument.participant</t>
   </si>
   <si>
-    <t>EnteteDocument.prescription</t>
+    <t>FRLMEnteteDocument.prescription</t>
   </si>
   <si>
     <t>ClinicalDocument.inFulfillmentOf</t>
   </si>
   <si>
-    <t>EnteteDocument.evenement</t>
+    <t>FRLMEnteteDocument.evenement</t>
   </si>
   <si>
     <t>ClinicalDocument.documentationOf</t>
   </si>
   <si>
-    <t>EnteteDocument.documentDeReference</t>
+    <t>FRLMEnteteDocument.documentDeReference</t>
   </si>
   <si>
     <t>ClinicalDocument.relatedDocument</t>
   </si>
   <si>
-    <t>EnteteDocument.consentementAssocie</t>
+    <t>FRLMEnteteDocument.consentementAssocie</t>
   </si>
   <si>
     <t>ClinicalDocument.authorization</t>
   </si>
   <si>
-    <t>EnteteDocument.priseEncharge</t>
+    <t>FRLMEnteteDocument.priseEncharge</t>
   </si>
   <si>
     <t>ClinicalDocument.componentOf</t>

--- a/main/ig/mappingmodelemetierCDAFHIR.xlsx
+++ b/main/ig/mappingmodelemetierCDAFHIR.xlsx
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-21T16:49:23+00:00</t>
+    <t>2025-10-21T17:18:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/mappingmodelemetierCDAFHIR.xlsx
+++ b/main/ig/mappingmodelemetierCDAFHIR.xlsx
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-21T17:18:21+00:00</t>
+    <t>2025-10-22T08:56:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
